--- a/테크니션_평가표.xlsx
+++ b/테크니션_평가표.xlsx
@@ -2476,14 +2476,14 @@
     <row r="26">
       <c r="B26" s="30" t="inlineStr">
         <is>
-          <t>비엔이 축적한 자산을 공유합니다. 자유롭게 활용하고 나누실 수 있습니다.</t>
+          <t>비엔이 축적한 자산을 공유합니다.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>다른 곳에 공유하실 때는 원본 페이지 주소를 함께 남겨주세요.</t>
+          <t>우리 병원에 맞게 수정해서 사용하시고, 다른 곳에 공유하실 때는 원본 페이지 주소를 함께 남겨주세요.</t>
         </is>
       </c>
     </row>
